--- a/data/ams_weekly_data/White_Mulberry/ads_report_week34.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week34.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -2115,7 +2103,7 @@
         <v>131</v>
       </c>
       <c r="F60" t="n">
-        <v>67506</v>
+        <v>67505</v>
       </c>
       <c r="G60" t="n">
         <v>2961.86</v>
@@ -3263,7 +3251,7 @@
         <v>82</v>
       </c>
       <c r="F101" t="n">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="G101" t="n">
         <v>18083.07</v>
@@ -3455,42 +3443,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4403,51 +4391,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -4726,23 +4714,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22467</v>
+        <v>9803</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>1603.764674605468</v>
+        <v>699.766</v>
       </c>
       <c r="G10" t="n">
-        <v>4795.810227602191</v>
+        <v>2092.542</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4759,20 +4747,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10720</v>
+        <v>9803</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>765.2465902213806</v>
+        <v>699.766</v>
       </c>
       <c r="G11" t="n">
-        <v>2288.351578091859</v>
+        <v>2092.542</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -4792,20 +4780,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15827</v>
+        <v>9803</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>1129.818735173151</v>
+        <v>699.766</v>
       </c>
       <c r="G12" t="n">
-        <v>3378.548194305949</v>
+        <v>2092.542</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -4820,28 +4808,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>9803</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>7.311666666666667</v>
+        <v>699.766</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2092.542</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -4853,28 +4841,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>9803</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>7.311666666666667</v>
+        <v>699.766</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2092.542</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4891,7 +4879,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4924,7 +4912,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -4957,7 +4945,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4990,7 +4978,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5018,28 +5006,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12375</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1606.116201174661</v>
+        <v>7.311666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5051,30 +5039,63 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.311666666666667</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>13501</v>
-      </c>
-      <c r="E20" t="n">
-        <v>131</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1752.183798825338</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2541.530000000001</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25876</v>
+      </c>
+      <c r="E21" t="n">
+        <v>251</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3358.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4871.190000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week34.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week34.xlsx
@@ -4391,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4714,23 +4714,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9803</v>
+        <v>22466</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>699.766</v>
+        <v>1603.764674605468</v>
       </c>
       <c r="G10" t="n">
-        <v>2092.542</v>
+        <v>4795.810227602191</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4747,20 +4747,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9803</v>
+        <v>10720</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>699.766</v>
+        <v>765.2465902213806</v>
       </c>
       <c r="G11" t="n">
-        <v>2092.542</v>
+        <v>2288.35157809186</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -4780,20 +4780,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9803</v>
+        <v>15827</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>699.766</v>
+        <v>1129.818735173151</v>
       </c>
       <c r="G12" t="n">
-        <v>2092.542</v>
+        <v>3378.548194305949</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -4808,28 +4808,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9803</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>699.766</v>
+        <v>7.311666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>2092.542</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -4841,28 +4841,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9803</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>699.766</v>
+        <v>7.311666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>2092.542</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5006,28 +5006,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>12375</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F19" t="n">
-        <v>7.311666666666667</v>
+        <v>1606.116201174661</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5039,63 +5039,30 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>13501</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F20" t="n">
-        <v>7.311666666666667</v>
+        <v>1752.183798825338</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2541.530000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>25876</v>
-      </c>
-      <c r="E21" t="n">
-        <v>251</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3358.3</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4871.190000000001</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
